--- a/artfynd/A 31148-2024 artfynd.xlsx
+++ b/artfynd/A 31148-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>119796745</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
